--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/dic-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/dic-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/dic-2025.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Superintendencia de Electricidad y Combustibles</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Adulto Mayor</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pasos Fronterizos</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/dic-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/dic-2025.xlsx
@@ -562,7 +562,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1790,7 +1862,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1851,7 +1927,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1992,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2034,7 +2118,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2095,7 +2183,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2156,7 +2248,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2217,7 +2313,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2278,7 +2378,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2339,7 +2443,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2400,7 +2508,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2461,7 +2573,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2522,7 +2638,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2583,7 +2703,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2644,7 +2768,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2705,7 +2833,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2766,7 +2898,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2827,7 +2963,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2888,7 +3028,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2949,7 +3093,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3010,7 +3158,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3071,7 +3223,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3132,7 +3288,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3193,7 +3353,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3254,7 +3418,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3315,7 +3483,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3376,7 +3548,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3437,7 +3613,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3498,7 +3678,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3559,7 +3743,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3681,7 +3869,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3807,7 +3999,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3868,7 +4064,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3929,7 +4129,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3990,7 +4194,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4051,7 +4259,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4112,7 +4324,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4173,7 +4389,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4234,7 +4454,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4295,7 +4519,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4356,7 +4584,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4417,7 +4649,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4478,7 +4714,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4539,7 +4779,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
